--- a/nba2k26_editor/Offsets/ImportStaff.xlsx
+++ b/nba2k26_editor/Offsets/ImportStaff.xlsx
@@ -10,7 +10,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staff Vitals" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staff Attributes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staff Style" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staff Coaching" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,138 +427,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Salary</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Years Left</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>*Unique Photo ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Face ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>First Name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Height</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Last Name</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Position</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Vitals - ARM_SCALE</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Vitals - BODYLENGTH</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Vitals - BODY_SHAPE</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Vitals - CURRENT_TEAM</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Vitals - EYE_COLOR</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Vitals - FIRSTNAME</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Vitals - GENDER</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Vitals - HAIR_LENGTH</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Vitals - HAND_SCALE</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Vitals - HEIGHT_CM</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Vitals - LASTNAME</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Vitals - LOWER_SCALE</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Vitals - NECK_HEAD_SCALE</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Vitals - PERSONALITY</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Vitals - POSITION</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Vitals - SALARY</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Vitals - SHOULDERWIDTH</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Vitals - SKINCOLOR</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Vitals - SKINTYPE</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Vitals - WINGSPAN_CM</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Vitals - YEARS_IN_LEAGUE</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Vitals - YEARS_LEFT</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>*Unique Photo ID</t>
         </is>
       </c>
     </row>
@@ -574,83 +483,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Staff Attributes - BUSINESS</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Staff Attributes - CONTRACTS</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Staff Attributes - DEFENSE</t>
+          <t>Charisma</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Staff Attributes - MAX_BUSINESS</t>
+          <t>Defensive Coaching</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Staff Attributes - MAX_CONTRACTS</t>
+          <t>Offensive Coaching</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Staff Attributes - MAX_DEFENSE</t>
+          <t>Potential</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Staff Attributes - MAX_OFFENSE</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Attributes - MAX_SCOUTING</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Attributes - MAX_TRADING</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Attributes - MAX_TRAINING</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Attributes - OFFENSE</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Attributes - POTENTIAL</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Attributes - SCOUTING</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Attributes - TRADING</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Attributes - TRAINING</t>
+          <t>Sports Medicine</t>
         </is>
       </c>
     </row>
@@ -665,119 +534,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Balanced Proficiency</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Defense Proficiency</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Grit &amp; Grind Proficiency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Pace &amp;Space Proficiency</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Perimeter Centric Proficiency</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Post Centric Proficiency</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Seven Seconds Proficiency</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Defense Proficiency</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Grit &amp; Grind Proficiency</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Pace &amp;Space Proficiency</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Perimeter Centric Proficiency</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Post Centric Proficiency</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Style - ACTIVE_SYSTEM</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Staff Style - BALANCED_PROFICIENCY</t>
+          <t>Triangle Proficiency</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Staff Style - GUARDS_VS_FORWARDS</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Style - INSIDE_VS_OUTSIDE</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Style - OFFENSE_VS_DEFENSE</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Style - PERIMETER_CENTERIC_PROFICIENCY</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Style - PREFERRED_SYSTEM</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Style - STYLE_N#1</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Style - STYLE_N#2</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Style - STYLE_N#3</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Style - TRIANGLE_PROFICIENCY</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Coaching - BENCH_UTILIZATION</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Staff Coaching - PLAYBOOK</t>
+          <t>Current Team</t>
         </is>
       </c>
     </row>
